--- a/CT_2020_harvest_estimates_cost_servings_community_sum.xlsx
+++ b/CT_2020_harvest_estimates_cost_servings_community_sum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariegutgesell/Desktop/Wild Foods Repo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariegutgesell/LocalRepos/Wild Foods Repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{833BE06E-EAF5-C942-9E22-A0A191A600FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF74319F-17C7-1E42-B742-0405A7DDF4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16600" xr2:uid="{EBB03A24-0A84-7241-B627-1F94F7004BEC}"/>
+    <workbookView xWindow="28840" yWindow="500" windowWidth="33560" windowHeight="19280" xr2:uid="{EBB03A24-0A84-7241-B627-1F94F7004BEC}"/>
   </bookViews>
   <sheets>
     <sheet name="CT_2020_harvest_estimates_cost_" sheetId="1" r:id="rId1"/>
@@ -1108,72 +1108,72 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C2">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>8458</v>
       </c>
       <c r="E2" s="3">
-        <v>6806.5355714322804</v>
+        <v>670534.57241456094</v>
       </c>
       <c r="F2" s="3">
-        <v>241161.041382747</v>
+        <v>27733561.654179499</v>
       </c>
       <c r="G2" s="3">
-        <v>0.24116104138274699</v>
+        <v>27.7335616541795</v>
       </c>
       <c r="H2" s="3">
-        <v>45376.903809548603</v>
+        <v>4470230.4827637402</v>
       </c>
       <c r="I2" s="3">
-        <v>4087.47527767368</v>
+        <v>3278.97394823594</v>
       </c>
       <c r="J2" s="3">
-        <v>769.10006456862004</v>
+        <v>528.52098401084595</v>
       </c>
       <c r="K2" s="3">
-        <v>115.365009685293</v>
+        <v>79.278147601626898</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="D3">
-        <v>344</v>
+        <v>3043</v>
       </c>
       <c r="E3" s="3">
-        <v>14272.592364861601</v>
+        <v>222685.55412984599</v>
       </c>
       <c r="F3" s="3">
-        <v>546652.26677333296</v>
+        <v>8154147.8171441201</v>
       </c>
       <c r="G3" s="3">
-        <v>0.54665226677333301</v>
+        <v>8.1541478171441195</v>
       </c>
       <c r="H3" s="3">
-        <v>95150.615765744005</v>
+        <v>1484570.36086564</v>
       </c>
       <c r="I3" s="3">
-        <v>1589.1054266666699</v>
+        <v>2679.6410835176198</v>
       </c>
       <c r="J3" s="3">
-        <v>276.60062722599997</v>
+        <v>487.86406863806701</v>
       </c>
       <c r="K3" s="3">
-        <v>41.490094083899997</v>
+        <v>73.179610295710106</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1181,104 +1181,104 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>2014</v>
+        <v>1992</v>
       </c>
       <c r="D4">
-        <v>2609</v>
+        <v>3985</v>
       </c>
       <c r="E4" s="3">
-        <v>137454.73530513499</v>
+        <v>186974.58508990801</v>
       </c>
       <c r="F4" s="3">
-        <v>5805861.7341173999</v>
+        <v>7202626.35156429</v>
       </c>
       <c r="G4" s="3">
-        <v>5.8058617341173999</v>
+        <v>7.2026263515642901</v>
       </c>
       <c r="H4" s="3">
-        <v>916364.90203423705</v>
+        <v>1246497.23393272</v>
       </c>
       <c r="I4" s="3">
-        <v>2225.3207106620898</v>
+        <v>1807.4344671428601</v>
       </c>
       <c r="J4" s="3">
-        <v>351.23223535233302</v>
+        <v>312.79729835199998</v>
       </c>
       <c r="K4" s="3">
-        <v>52.684835302849898</v>
+        <v>46.919594752800002</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C5">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="D5">
-        <v>161</v>
+        <v>2127</v>
       </c>
       <c r="E5" s="3">
-        <v>8088.6224350931998</v>
+        <v>161569.85563409701</v>
       </c>
       <c r="F5" s="3">
-        <v>300870.10884</v>
+        <v>6496128.7851436501</v>
       </c>
       <c r="G5" s="3">
-        <v>0.30087010883999998</v>
+        <v>6.4961287851436502</v>
       </c>
       <c r="H5" s="3">
-        <v>53924.149567287997</v>
+        <v>1077132.3708939799</v>
       </c>
       <c r="I5" s="3">
-        <v>1868.7584400000001</v>
+        <v>3054.12730848315</v>
       </c>
       <c r="J5" s="3">
-        <v>334.93260600799999</v>
+        <v>506.40920117253302</v>
       </c>
       <c r="K5" s="3">
-        <v>50.239890901199999</v>
+        <v>75.961380175879896</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C6">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="D6">
-        <v>228</v>
+        <v>931</v>
       </c>
       <c r="E6" s="3">
-        <v>8976.7744392479999</v>
+        <v>144804.78283956301</v>
       </c>
       <c r="F6" s="3">
-        <v>361200.97440000001</v>
+        <v>6167484.76026667</v>
       </c>
       <c r="G6" s="3">
-        <v>0.36120097439999999</v>
+        <v>6.16748476026667</v>
       </c>
       <c r="H6" s="3">
-        <v>59845.162928320002</v>
+        <v>965365.21893042</v>
       </c>
       <c r="I6" s="3">
-        <v>1584.2148</v>
+        <v>6624.5808380952403</v>
       </c>
       <c r="J6" s="3">
-        <v>262.47878477333302</v>
+        <v>1036.9121578199999</v>
       </c>
       <c r="K6" s="3">
-        <v>39.371817716000002</v>
+        <v>155.53682367299999</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1286,34 +1286,34 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>2014</v>
       </c>
       <c r="D7">
-        <v>247</v>
+        <v>2609</v>
       </c>
       <c r="E7" s="3">
-        <v>28348.045774395901</v>
+        <v>137454.73530513499</v>
       </c>
       <c r="F7" s="3">
-        <v>953384.86553462897</v>
+        <v>5805861.7341173999</v>
       </c>
       <c r="G7" s="3">
-        <v>0.95338486553462898</v>
+        <v>5.8058617341173999</v>
       </c>
       <c r="H7" s="3">
-        <v>188986.97182930601</v>
+        <v>916364.90203423705</v>
       </c>
       <c r="I7" s="3">
-        <v>3859.8577552009301</v>
+        <v>2225.3207106620898</v>
       </c>
       <c r="J7" s="3">
-        <v>765.12944060447899</v>
+        <v>351.23223535233302</v>
       </c>
       <c r="K7" s="3">
-        <v>114.769416090672</v>
+        <v>52.684835302849898</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1321,174 +1321,174 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="D8">
-        <v>162</v>
+        <v>2717</v>
       </c>
       <c r="E8" s="3">
-        <v>16020.966934427801</v>
+        <v>119420.574474201</v>
       </c>
       <c r="F8" s="3">
-        <v>595807.79989863001</v>
+        <v>4453879.2917666696</v>
       </c>
       <c r="G8" s="3">
-        <v>0.59580779989862998</v>
+        <v>4.4538792917666701</v>
       </c>
       <c r="H8" s="3">
-        <v>106806.446229519</v>
+        <v>796137.16316134005</v>
       </c>
       <c r="I8" s="3">
-        <v>3677.8259253001902</v>
+        <v>1639.2636333333301</v>
       </c>
       <c r="J8" s="3">
-        <v>659.29905079949901</v>
+        <v>293.02067102000001</v>
       </c>
       <c r="K8" s="3">
-        <v>98.894857619924807</v>
+        <v>43.953100653</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="D9">
-        <v>2717</v>
+        <v>1036</v>
       </c>
       <c r="E9" s="3">
-        <v>119420.574474201</v>
+        <v>108974.841144708</v>
       </c>
       <c r="F9" s="3">
-        <v>4453879.2917666696</v>
+        <v>4686447.898</v>
       </c>
       <c r="G9" s="3">
-        <v>4.4538792917666701</v>
+        <v>4.6864478979999999</v>
       </c>
       <c r="H9" s="3">
-        <v>796137.16316134005</v>
+        <v>726498.94096471998</v>
       </c>
       <c r="I9" s="3">
-        <v>1639.2636333333301</v>
+        <v>4523.5983571428596</v>
       </c>
       <c r="J9" s="3">
-        <v>293.02067102000001</v>
+        <v>701.25380401999996</v>
       </c>
       <c r="K9" s="3">
-        <v>43.953100653</v>
+        <v>105.188070603</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C10">
-        <v>2014</v>
+        <v>1997</v>
       </c>
       <c r="D10">
-        <v>90</v>
+        <v>720</v>
       </c>
       <c r="E10" s="3">
-        <v>11984.32938307</v>
+        <v>104618.72146017601</v>
       </c>
       <c r="F10" s="3">
-        <v>540045.72983874904</v>
+        <v>4511613.0387428598</v>
       </c>
       <c r="G10" s="3">
-        <v>0.54004572983874899</v>
+        <v>4.5116130387428601</v>
       </c>
       <c r="H10" s="3">
-        <v>79895.529220466298</v>
+        <v>697458.14306784002</v>
       </c>
       <c r="I10" s="3">
-        <v>6000.5081093194403</v>
+        <v>6266.1292204761903</v>
       </c>
       <c r="J10" s="3">
-        <v>887.72810244962602</v>
+        <v>968.69186537200005</v>
       </c>
       <c r="K10" s="3">
-        <v>133.15921536744401</v>
+        <v>145.30377980579999</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C11">
-        <v>1992</v>
+        <v>2012</v>
       </c>
       <c r="D11">
-        <v>3985</v>
+        <v>1657</v>
       </c>
       <c r="E11" s="3">
-        <v>186974.58508990801</v>
+        <v>101165.704184314</v>
       </c>
       <c r="F11" s="3">
-        <v>7202626.35156429</v>
+        <v>4020501.9389333301</v>
       </c>
       <c r="G11" s="3">
-        <v>7.2026263515642901</v>
+        <v>4.0205019389333296</v>
       </c>
       <c r="H11" s="3">
-        <v>1246497.23393272</v>
+        <v>674438.02789542696</v>
       </c>
       <c r="I11" s="3">
-        <v>1807.4344671428601</v>
+        <v>2426.3741333333301</v>
       </c>
       <c r="J11" s="3">
-        <v>312.79729835199998</v>
+        <v>407.02355334666697</v>
       </c>
       <c r="K11" s="3">
-        <v>46.919594752800002</v>
+        <v>61.053533002000002</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C12">
-        <v>1990</v>
+        <v>2012</v>
       </c>
       <c r="D12">
-        <v>272</v>
+        <v>380</v>
       </c>
       <c r="E12" s="3">
-        <v>9878.8063699247996</v>
+        <v>91422.449358240003</v>
       </c>
       <c r="F12" s="3">
-        <v>343102.74208</v>
+        <v>3688911.15828571</v>
       </c>
       <c r="G12" s="3">
-        <v>0.34310274208000002</v>
+        <v>3.6889111582857099</v>
       </c>
       <c r="H12" s="3">
-        <v>65858.709132831995</v>
+        <v>609482.99572160002</v>
       </c>
       <c r="I12" s="3">
-        <v>1261.40714</v>
+        <v>9707.6609428571392</v>
       </c>
       <c r="J12" s="3">
-        <v>242.127607106</v>
+        <v>1603.9026203200001</v>
       </c>
       <c r="K12" s="3">
-        <v>36.319141065899998</v>
+        <v>240.58539304799999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1496,34 +1496,34 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C13">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="D13">
-        <v>357</v>
+        <v>657</v>
       </c>
       <c r="E13" s="3">
-        <v>29504.097143597999</v>
+        <v>77911.958728638696</v>
       </c>
       <c r="F13" s="3">
-        <v>1359864.9367</v>
+        <v>3858107.7875498701</v>
       </c>
       <c r="G13" s="3">
-        <v>1.3598649367</v>
+        <v>3.8581077875498702</v>
       </c>
       <c r="H13" s="3">
-        <v>196693.98095731999</v>
+        <v>519413.05819092499</v>
       </c>
       <c r="I13" s="3">
-        <v>3809.1454809523798</v>
+        <v>5872.3101789191396</v>
       </c>
       <c r="J13" s="3">
-        <v>550.96353209333301</v>
+        <v>790.58304138649203</v>
       </c>
       <c r="K13" s="3">
-        <v>82.644529813999995</v>
+        <v>118.587456207974</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1531,34 +1531,34 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>1998</v>
+        <v>1987</v>
       </c>
       <c r="D14">
-        <v>127</v>
+        <v>655</v>
       </c>
       <c r="E14" s="3">
-        <v>15907.960687888501</v>
+        <v>71551.316055950505</v>
       </c>
       <c r="F14" s="3">
-        <v>680348.73763428605</v>
+        <v>3425848.0220952402</v>
       </c>
       <c r="G14" s="3">
-        <v>0.68034873763428605</v>
+        <v>3.4258480220952401</v>
       </c>
       <c r="H14" s="3">
-        <v>106053.07125259</v>
+        <v>477008.77370633697</v>
       </c>
       <c r="I14" s="3">
-        <v>5357.0766742857104</v>
+        <v>5230.3023238095202</v>
       </c>
       <c r="J14" s="3">
-        <v>835.06355316999998</v>
+        <v>728.25766978066599</v>
       </c>
       <c r="K14" s="3">
-        <v>125.25953297549999</v>
+        <v>109.2386504671</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -1566,34 +1566,34 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C15">
-        <v>1997</v>
+        <v>1987</v>
       </c>
       <c r="D15">
-        <v>1036</v>
+        <v>1454</v>
       </c>
       <c r="E15" s="3">
-        <v>108974.841144708</v>
+        <v>46252.369448377402</v>
       </c>
       <c r="F15" s="3">
-        <v>4686447.898</v>
+        <v>2259605.6709495201</v>
       </c>
       <c r="G15" s="3">
-        <v>4.6864478979999999</v>
+        <v>2.25960567094952</v>
       </c>
       <c r="H15" s="3">
-        <v>726498.94096471998</v>
+        <v>308349.12965584901</v>
       </c>
       <c r="I15" s="3">
-        <v>4523.5983571428596</v>
+        <v>1554.06167190476</v>
       </c>
       <c r="J15" s="3">
-        <v>701.25380401999996</v>
+        <v>212.06955272066699</v>
       </c>
       <c r="K15" s="3">
-        <v>105.188070603</v>
+        <v>31.810432908100001</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -1601,34 +1601,34 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>543</v>
       </c>
       <c r="E16" s="3">
-        <v>4346.095293155</v>
+        <v>44112.447652581002</v>
       </c>
       <c r="F16" s="3">
-        <v>161604.11989285701</v>
+        <v>2103634.8812185698</v>
       </c>
       <c r="G16" s="3">
-        <v>0.161604119892857</v>
+        <v>2.1036348812185701</v>
       </c>
       <c r="H16" s="3">
-        <v>28973.968621033298</v>
+        <v>294082.98435053998</v>
       </c>
       <c r="I16" s="3">
-        <v>6464.1647957142804</v>
+        <v>3874.09738714286</v>
       </c>
       <c r="J16" s="3">
-        <v>1158.9587448413299</v>
+        <v>541.58928977999994</v>
       </c>
       <c r="K16" s="3">
-        <v>173.84381172619999</v>
+        <v>81.238393466999995</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -1636,34 +1636,34 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C17">
-        <v>1987</v>
+        <v>1998</v>
       </c>
       <c r="D17">
-        <v>24</v>
+        <v>476</v>
       </c>
       <c r="E17" s="3">
-        <v>2857.8496553375999</v>
+        <v>38695.384486466399</v>
       </c>
       <c r="F17" s="3">
-        <v>151301.63959999999</v>
+        <v>1532045.62745333</v>
       </c>
       <c r="G17" s="3">
-        <v>0.15130163960000001</v>
+        <v>1.5320456274533301</v>
       </c>
       <c r="H17" s="3">
-        <v>19052.331035584</v>
+        <v>257969.22990977601</v>
       </c>
       <c r="I17" s="3">
-        <v>6304.2349833333301</v>
+        <v>3218.5832509523798</v>
       </c>
       <c r="J17" s="3">
-        <v>793.847126482666</v>
+        <v>541.95216367600005</v>
       </c>
       <c r="K17" s="3">
-        <v>119.0770689724</v>
+        <v>81.292824551400003</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -1671,34 +1671,34 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C18">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="D18">
-        <v>23</v>
+        <v>384</v>
       </c>
       <c r="E18" s="3">
-        <v>1953.1959607622</v>
+        <v>37824.802344072501</v>
       </c>
       <c r="F18" s="3">
-        <v>86512.378096666696</v>
+        <v>1632750.3408613</v>
       </c>
       <c r="G18" s="3">
-        <v>8.6512378096666703E-2</v>
+        <v>1.6327503408613</v>
       </c>
       <c r="H18" s="3">
-        <v>13021.306405081301</v>
+        <v>252165.34896048301</v>
       </c>
       <c r="I18" s="3">
-        <v>3761.40774333333</v>
+        <v>4251.9540126596503</v>
       </c>
       <c r="J18" s="3">
-        <v>566.14375674266705</v>
+        <v>656.68059625125795</v>
       </c>
       <c r="K18" s="3">
-        <v>84.921563511399995</v>
+        <v>98.502089437688795</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -1706,69 +1706,69 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="D19">
-        <v>655</v>
+        <v>357</v>
       </c>
       <c r="E19" s="3">
-        <v>71551.316055950505</v>
+        <v>29504.097143597999</v>
       </c>
       <c r="F19" s="3">
-        <v>3425848.0220952402</v>
+        <v>1359864.9367</v>
       </c>
       <c r="G19" s="3">
-        <v>3.4258480220952401</v>
+        <v>1.3598649367</v>
       </c>
       <c r="H19" s="3">
-        <v>477008.77370633697</v>
+        <v>196693.98095731999</v>
       </c>
       <c r="I19" s="3">
-        <v>5230.3023238095202</v>
+        <v>3809.1454809523798</v>
       </c>
       <c r="J19" s="3">
-        <v>728.25766978066599</v>
+        <v>550.96353209333301</v>
       </c>
       <c r="K19" s="3">
-        <v>109.2386504671</v>
+        <v>82.644529813999995</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D20">
-        <v>1657</v>
+        <v>247</v>
       </c>
       <c r="E20" s="3">
-        <v>101165.704184314</v>
+        <v>28348.045774395901</v>
       </c>
       <c r="F20" s="3">
-        <v>4020501.9389333301</v>
+        <v>953384.86553462897</v>
       </c>
       <c r="G20" s="3">
-        <v>4.0205019389333296</v>
+        <v>0.95338486553462898</v>
       </c>
       <c r="H20" s="3">
-        <v>674438.02789542696</v>
+        <v>188986.97182930601</v>
       </c>
       <c r="I20" s="3">
-        <v>2426.3741333333301</v>
+        <v>3859.8577552009301</v>
       </c>
       <c r="J20" s="3">
-        <v>407.02355334666697</v>
+        <v>765.12944060447899</v>
       </c>
       <c r="K20" s="3">
-        <v>61.053533002000002</v>
+        <v>114.769416090672</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -1776,34 +1776,34 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C21">
-        <v>1998</v>
+        <v>1987</v>
       </c>
       <c r="D21">
-        <v>65</v>
+        <v>1164</v>
       </c>
       <c r="E21" s="3">
-        <v>4990.3778955030002</v>
+        <v>25395.911048507998</v>
       </c>
       <c r="F21" s="3">
-        <v>192256.54026428601</v>
+        <v>1098444.83809143</v>
       </c>
       <c r="G21" s="3">
-        <v>0.19225654026428601</v>
+        <v>1.09844483809143</v>
       </c>
       <c r="H21" s="3">
-        <v>33269.18597002</v>
+        <v>169306.07365671999</v>
       </c>
       <c r="I21" s="3">
-        <v>2957.7929271428602</v>
+        <v>943.68113238095202</v>
       </c>
       <c r="J21" s="3">
-        <v>511.83363030800001</v>
+        <v>145.45195331333301</v>
       </c>
       <c r="K21" s="3">
-        <v>76.775044546199993</v>
+        <v>21.817792997000002</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -1811,34 +1811,34 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C22">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D22">
-        <v>931</v>
+        <v>87</v>
       </c>
       <c r="E22" s="3">
-        <v>144804.78283956301</v>
+        <v>17820.347807210001</v>
       </c>
       <c r="F22" s="3">
-        <v>6167484.76026667</v>
+        <v>541971.96684274904</v>
       </c>
       <c r="G22" s="3">
-        <v>6.16748476026667</v>
+        <v>0.54197196684274895</v>
       </c>
       <c r="H22" s="3">
-        <v>965365.21893042</v>
+        <v>118802.31871473401</v>
       </c>
       <c r="I22" s="3">
-        <v>6624.5808380952403</v>
+        <v>6229.5628372729798</v>
       </c>
       <c r="J22" s="3">
-        <v>1036.9121578199999</v>
+        <v>1365.5438932728</v>
       </c>
       <c r="K22" s="3">
-        <v>155.53682367299999</v>
+        <v>204.83158399092</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -1846,69 +1846,69 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C23">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="D23">
-        <v>380</v>
+        <v>116</v>
       </c>
       <c r="E23" s="3">
-        <v>91422.449358240003</v>
+        <v>17360.358920704799</v>
       </c>
       <c r="F23" s="3">
-        <v>3688911.15828571</v>
+        <v>843619.71903238096</v>
       </c>
       <c r="G23" s="3">
-        <v>3.6889111582857099</v>
+        <v>0.84361971903238098</v>
       </c>
       <c r="H23" s="3">
-        <v>609482.99572160002</v>
+        <v>115735.726138032</v>
       </c>
       <c r="I23" s="3">
-        <v>9707.6609428571392</v>
+        <v>7272.5837847618996</v>
       </c>
       <c r="J23" s="3">
-        <v>1603.9026203200001</v>
+        <v>997.72177705199999</v>
       </c>
       <c r="K23" s="3">
-        <v>240.58539304799999</v>
+        <v>149.6582665578</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>1987</v>
+        <v>2014</v>
       </c>
       <c r="D24">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3">
-        <v>7517.5859286528002</v>
+        <v>16020.966934427801</v>
       </c>
       <c r="F24" s="3">
-        <v>306488.07065142901</v>
+        <v>595807.79989863001</v>
       </c>
       <c r="G24" s="3">
-        <v>0.30648807065142902</v>
+        <v>0.59580779989862998</v>
       </c>
       <c r="H24" s="3">
-        <v>50117.239524352</v>
+        <v>106806.446229519</v>
       </c>
       <c r="I24" s="3">
-        <v>6385.1681385714301</v>
+        <v>3677.8259253001902</v>
       </c>
       <c r="J24" s="3">
-        <v>1044.1091567573301</v>
+        <v>659.29905079949901</v>
       </c>
       <c r="K24" s="3">
-        <v>156.6163735136</v>
+        <v>98.894857619924807</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -1916,34 +1916,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C25">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D25">
-        <v>543</v>
+        <v>127</v>
       </c>
       <c r="E25" s="3">
-        <v>44112.447652581002</v>
+        <v>15907.960687888501</v>
       </c>
       <c r="F25" s="3">
-        <v>2103634.8812185698</v>
+        <v>680348.73763428605</v>
       </c>
       <c r="G25" s="3">
-        <v>2.1036348812185701</v>
+        <v>0.68034873763428605</v>
       </c>
       <c r="H25" s="3">
-        <v>294082.98435053998</v>
+        <v>106053.07125259</v>
       </c>
       <c r="I25" s="3">
-        <v>3874.09738714286</v>
+        <v>5357.0766742857104</v>
       </c>
       <c r="J25" s="3">
-        <v>541.58928977999994</v>
+        <v>835.06355316999998</v>
       </c>
       <c r="K25" s="3">
-        <v>81.238393466999995</v>
+        <v>125.25953297549999</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -1951,34 +1951,34 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C26">
-        <v>1998</v>
+        <v>1987</v>
       </c>
       <c r="D26">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3">
-        <v>6150.5764594889997</v>
+        <v>15785.8127985712</v>
       </c>
       <c r="F26" s="3">
-        <v>298753.29621428601</v>
+        <v>696409.31705333304</v>
       </c>
       <c r="G26" s="3">
-        <v>0.29875329621428598</v>
+        <v>0.69640931705333298</v>
       </c>
       <c r="H26" s="3">
-        <v>41003.843063259999</v>
+        <v>105238.75199047499</v>
       </c>
       <c r="I26" s="3">
-        <v>9958.44320714286</v>
+        <v>7106.2175209523803</v>
       </c>
       <c r="J26" s="3">
-        <v>1366.7947687753301</v>
+        <v>1073.86481622933</v>
       </c>
       <c r="K26" s="3">
-        <v>205.01921531630001</v>
+        <v>161.0797224344</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -1986,104 +1986,104 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C27">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D27">
-        <v>720</v>
+        <v>142</v>
       </c>
       <c r="E27" s="3">
-        <v>104618.72146017601</v>
+        <v>15559.5518525678</v>
       </c>
       <c r="F27" s="3">
-        <v>4511613.0387428598</v>
+        <v>618920.78677999997</v>
       </c>
       <c r="G27" s="3">
-        <v>4.5116130387428601</v>
+        <v>0.61892078677999995</v>
       </c>
       <c r="H27" s="3">
-        <v>697458.14306784002</v>
+        <v>103730.345683785</v>
       </c>
       <c r="I27" s="3">
-        <v>6266.1292204761903</v>
+        <v>4358.5970900000002</v>
       </c>
       <c r="J27" s="3">
-        <v>968.69186537200005</v>
+        <v>730.49539213933303</v>
       </c>
       <c r="K27" s="3">
-        <v>145.30377980579999</v>
+        <v>109.5743088209</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>2014</v>
+        <v>1990</v>
       </c>
       <c r="D28">
-        <v>87</v>
+        <v>344</v>
       </c>
       <c r="E28" s="3">
-        <v>17820.347807210001</v>
+        <v>14272.592364861601</v>
       </c>
       <c r="F28" s="3">
-        <v>541971.96684274904</v>
+        <v>546652.26677333296</v>
       </c>
       <c r="G28" s="3">
-        <v>0.54197196684274895</v>
+        <v>0.54665226677333301</v>
       </c>
       <c r="H28" s="3">
-        <v>118802.31871473401</v>
+        <v>95150.615765744005</v>
       </c>
       <c r="I28" s="3">
-        <v>6229.5628372729798</v>
+        <v>1589.1054266666699</v>
       </c>
       <c r="J28" s="3">
-        <v>1365.5438932728</v>
+        <v>276.60062722599997</v>
       </c>
       <c r="K28" s="3">
-        <v>204.83158399092</v>
+        <v>41.490094083899997</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>1987</v>
+        <v>2014</v>
       </c>
       <c r="D29">
-        <v>1454</v>
+        <v>90</v>
       </c>
       <c r="E29" s="3">
-        <v>46252.369448377402</v>
+        <v>11984.32938307</v>
       </c>
       <c r="F29" s="3">
-        <v>2259605.6709495201</v>
+        <v>540045.72983874904</v>
       </c>
       <c r="G29" s="3">
-        <v>2.25960567094952</v>
+        <v>0.54004572983874899</v>
       </c>
       <c r="H29" s="3">
-        <v>308349.12965584901</v>
+        <v>79895.529220466298</v>
       </c>
       <c r="I29" s="3">
-        <v>1554.06167190476</v>
+        <v>6000.5081093194403</v>
       </c>
       <c r="J29" s="3">
-        <v>212.06955272066699</v>
+        <v>887.72810244962602</v>
       </c>
       <c r="K29" s="3">
-        <v>31.810432908100001</v>
+        <v>133.15921536744401</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -2091,69 +2091,69 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C30">
-        <v>1998</v>
+        <v>1987</v>
       </c>
       <c r="D30">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="E30" s="3">
-        <v>15559.5518525678</v>
+        <v>11029.778865105</v>
       </c>
       <c r="F30" s="3">
-        <v>618920.78677999997</v>
+        <v>474737.56285428599</v>
       </c>
       <c r="G30" s="3">
-        <v>0.61892078677999995</v>
+        <v>0.47473756285428598</v>
       </c>
       <c r="H30" s="3">
-        <v>103730.345683785</v>
+        <v>73531.859100700007</v>
       </c>
       <c r="I30" s="3">
-        <v>4358.5970900000002</v>
+        <v>6086.3790109523798</v>
       </c>
       <c r="J30" s="3">
-        <v>730.49539213933303</v>
+        <v>942.71614231666695</v>
       </c>
       <c r="K30" s="3">
-        <v>109.5743088209</v>
+        <v>141.40742134749999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C31">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="D31">
-        <v>98</v>
+        <v>272</v>
       </c>
       <c r="E31" s="3">
-        <v>15785.8127985712</v>
+        <v>9878.8063699247996</v>
       </c>
       <c r="F31" s="3">
-        <v>696409.31705333304</v>
+        <v>343102.74208</v>
       </c>
       <c r="G31" s="3">
-        <v>0.69640931705333298</v>
+        <v>0.34310274208000002</v>
       </c>
       <c r="H31" s="3">
-        <v>105238.75199047499</v>
+        <v>65858.709132831995</v>
       </c>
       <c r="I31" s="3">
-        <v>7106.2175209523803</v>
+        <v>1261.40714</v>
       </c>
       <c r="J31" s="3">
-        <v>1073.86481622933</v>
+        <v>242.127607106</v>
       </c>
       <c r="K31" s="3">
-        <v>161.0797224344</v>
+        <v>36.319141065899998</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -2161,104 +2161,104 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C32">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="D32">
-        <v>3043</v>
+        <v>86</v>
       </c>
       <c r="E32" s="3">
-        <v>222685.55412984599</v>
+        <v>9604.0019684840008</v>
       </c>
       <c r="F32" s="3">
-        <v>8154147.8171441201</v>
+        <v>441763.34946666699</v>
       </c>
       <c r="G32" s="3">
-        <v>8.1541478171441195</v>
+        <v>0.44176334946666701</v>
       </c>
       <c r="H32" s="3">
-        <v>1484570.36086564</v>
+        <v>64026.6797898933</v>
       </c>
       <c r="I32" s="3">
-        <v>2679.6410835176198</v>
+        <v>5136.7831333333297</v>
       </c>
       <c r="J32" s="3">
-        <v>487.86406863806701</v>
+        <v>744.49627662666705</v>
       </c>
       <c r="K32" s="3">
-        <v>73.179610295710106</v>
+        <v>111.67444149400001</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C33">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="E33" s="3">
-        <v>1570.6089403620001</v>
+        <v>8976.7744392479999</v>
       </c>
       <c r="F33" s="3">
-        <v>58004.7033828571</v>
+        <v>361200.97440000001</v>
       </c>
       <c r="G33" s="3">
-        <v>5.8004703382857098E-2</v>
+        <v>0.36120097439999999</v>
       </c>
       <c r="H33" s="3">
-        <v>10470.72626908</v>
+        <v>59845.162928320002</v>
       </c>
       <c r="I33" s="3">
-        <v>4833.7252819047599</v>
+        <v>1584.2148</v>
       </c>
       <c r="J33" s="3">
-        <v>872.56052242333305</v>
+        <v>262.47878477333302</v>
       </c>
       <c r="K33" s="3">
-        <v>130.88407836350001</v>
+        <v>39.371817716000002</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="D34">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="E34" s="3">
-        <v>11029.778865105</v>
+        <v>8088.6224350931998</v>
       </c>
       <c r="F34" s="3">
-        <v>474737.56285428599</v>
+        <v>300870.10884</v>
       </c>
       <c r="G34" s="3">
-        <v>0.47473756285428598</v>
+        <v>0.30087010883999998</v>
       </c>
       <c r="H34" s="3">
-        <v>73531.859100700007</v>
+        <v>53924.149567287997</v>
       </c>
       <c r="I34" s="3">
-        <v>6086.3790109523798</v>
+        <v>1868.7584400000001</v>
       </c>
       <c r="J34" s="3">
-        <v>942.71614231666695</v>
+        <v>334.93260600799999</v>
       </c>
       <c r="K34" s="3">
-        <v>141.40742134749999</v>
+        <v>50.239890901199999</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C35">
-        <v>1996</v>
+        <v>1987</v>
       </c>
       <c r="D35">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E35" s="3">
-        <v>7362.2396137752003</v>
+        <v>7517.5859286528002</v>
       </c>
       <c r="F35" s="3">
-        <v>270528.82584</v>
+        <v>306488.07065142901</v>
       </c>
       <c r="G35" s="3">
-        <v>0.27052882583999999</v>
+        <v>0.30648807065142902</v>
       </c>
       <c r="H35" s="3">
-        <v>49081.597425168002</v>
+        <v>50117.239524352</v>
       </c>
       <c r="I35" s="3">
-        <v>7514.6896066666704</v>
+        <v>6385.1681385714301</v>
       </c>
       <c r="J35" s="3">
-        <v>1363.3777062546701</v>
+        <v>1044.1091567573301</v>
       </c>
       <c r="K35" s="3">
-        <v>204.5066559382</v>
+        <v>156.6163735136</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -2301,69 +2301,69 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="D36">
-        <v>384</v>
+        <v>36</v>
       </c>
       <c r="E36" s="3">
-        <v>37824.802344072501</v>
+        <v>7362.2396137752003</v>
       </c>
       <c r="F36" s="3">
-        <v>1632750.3408613</v>
+        <v>270528.82584</v>
       </c>
       <c r="G36" s="3">
-        <v>1.6327503408613</v>
+        <v>0.27052882583999999</v>
       </c>
       <c r="H36" s="3">
-        <v>252165.34896048301</v>
+        <v>49081.597425168002</v>
       </c>
       <c r="I36" s="3">
-        <v>4251.9540126596503</v>
+        <v>7514.6896066666704</v>
       </c>
       <c r="J36" s="3">
-        <v>656.68059625125795</v>
+        <v>1363.3777062546701</v>
       </c>
       <c r="K36" s="3">
-        <v>98.502089437688795</v>
+        <v>204.5066559382</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C37">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D37">
-        <v>8458</v>
+        <v>59</v>
       </c>
       <c r="E37" s="3">
-        <v>670534.57241456094</v>
+        <v>6806.5355714322804</v>
       </c>
       <c r="F37" s="3">
-        <v>27733561.654179499</v>
+        <v>241161.041382747</v>
       </c>
       <c r="G37" s="3">
-        <v>27.7335616541795</v>
+        <v>0.24116104138274699</v>
       </c>
       <c r="H37" s="3">
-        <v>4470230.4827637402</v>
+        <v>45376.903809548603</v>
       </c>
       <c r="I37" s="3">
-        <v>3278.97394823594</v>
+        <v>4087.47527767368</v>
       </c>
       <c r="J37" s="3">
-        <v>528.52098401084595</v>
+        <v>769.10006456862004</v>
       </c>
       <c r="K37" s="3">
-        <v>79.278147601626898</v>
+        <v>115.365009685293</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -2371,34 +2371,34 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C38">
-        <v>1987</v>
+        <v>1998</v>
       </c>
       <c r="D38">
-        <v>1164</v>
+        <v>30</v>
       </c>
       <c r="E38" s="3">
-        <v>25395.911048507998</v>
+        <v>6150.5764594889997</v>
       </c>
       <c r="F38" s="3">
-        <v>1098444.83809143</v>
+        <v>298753.29621428601</v>
       </c>
       <c r="G38" s="3">
-        <v>1.09844483809143</v>
+        <v>0.29875329621428598</v>
       </c>
       <c r="H38" s="3">
-        <v>169306.07365671999</v>
+        <v>41003.843063259999</v>
       </c>
       <c r="I38" s="3">
-        <v>943.68113238095202</v>
+        <v>9958.44320714286</v>
       </c>
       <c r="J38" s="3">
-        <v>145.45195331333301</v>
+        <v>1366.7947687753301</v>
       </c>
       <c r="K38" s="3">
-        <v>21.817792997000002</v>
+        <v>205.01921531630001</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -2406,34 +2406,34 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>1987</v>
+        <v>1998</v>
       </c>
       <c r="D39">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="E39" s="3">
-        <v>17360.358920704799</v>
+        <v>4990.3778955030002</v>
       </c>
       <c r="F39" s="3">
-        <v>843619.71903238096</v>
+        <v>192256.54026428601</v>
       </c>
       <c r="G39" s="3">
-        <v>0.84361971903238098</v>
+        <v>0.19225654026428601</v>
       </c>
       <c r="H39" s="3">
-        <v>115735.726138032</v>
+        <v>33269.18597002</v>
       </c>
       <c r="I39" s="3">
-        <v>7272.5837847618996</v>
+        <v>2957.7929271428602</v>
       </c>
       <c r="J39" s="3">
-        <v>997.72177705199999</v>
+        <v>511.83363030800001</v>
       </c>
       <c r="K39" s="3">
-        <v>149.6582665578</v>
+        <v>76.775044546199993</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -2441,34 +2441,34 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C40">
         <v>1998</v>
       </c>
       <c r="D40">
-        <v>476</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>38695.384486466399</v>
+        <v>4346.095293155</v>
       </c>
       <c r="F40" s="3">
-        <v>1532045.62745333</v>
+        <v>161604.11989285701</v>
       </c>
       <c r="G40" s="3">
-        <v>1.5320456274533301</v>
+        <v>0.161604119892857</v>
       </c>
       <c r="H40" s="3">
-        <v>257969.22990977601</v>
+        <v>28973.968621033298</v>
       </c>
       <c r="I40" s="3">
-        <v>3218.5832509523798</v>
+        <v>6464.1647957142804</v>
       </c>
       <c r="J40" s="3">
-        <v>541.95216367600005</v>
+        <v>1158.9587448413299</v>
       </c>
       <c r="K40" s="3">
-        <v>81.292824551400003</v>
+        <v>173.84381172619999</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -2476,34 +2476,34 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C41">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="D41">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="E41" s="3">
-        <v>9604.0019684840008</v>
+        <v>2857.8496553375999</v>
       </c>
       <c r="F41" s="3">
-        <v>441763.34946666699</v>
+        <v>151301.63959999999</v>
       </c>
       <c r="G41" s="3">
-        <v>0.44176334946666701</v>
+        <v>0.15130163960000001</v>
       </c>
       <c r="H41" s="3">
-        <v>64026.6797898933</v>
+        <v>19052.331035584</v>
       </c>
       <c r="I41" s="3">
-        <v>5136.7831333333297</v>
+        <v>6304.2349833333301</v>
       </c>
       <c r="J41" s="3">
-        <v>744.49627662666705</v>
+        <v>793.847126482666</v>
       </c>
       <c r="K41" s="3">
-        <v>111.67444149400001</v>
+        <v>119.0770689724</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -2511,34 +2511,34 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>1996</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E42" s="3">
-        <v>161.85990131080001</v>
+        <v>1953.1959607622</v>
       </c>
       <c r="F42" s="3">
-        <v>8002.3153219047599</v>
+        <v>86512.378096666696</v>
       </c>
       <c r="G42" s="3">
-        <v>8.0023153219047592E-3</v>
+        <v>8.6512378096666703E-2</v>
       </c>
       <c r="H42" s="3">
-        <v>1079.06600873867</v>
+        <v>13021.306405081301</v>
       </c>
       <c r="I42" s="3">
-        <v>4001.15766095238</v>
+        <v>3761.40774333333</v>
       </c>
       <c r="J42" s="3">
-        <v>539.53300436933296</v>
+        <v>566.14375674266705</v>
       </c>
       <c r="K42" s="3">
-        <v>80.929950655400006</v>
+        <v>84.921563511399995</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -2546,34 +2546,34 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C43">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="D43">
-        <v>2127</v>
+        <v>12</v>
       </c>
       <c r="E43" s="3">
-        <v>161569.85563409701</v>
+        <v>1570.6089403620001</v>
       </c>
       <c r="F43" s="3">
-        <v>6496128.7851436501</v>
+        <v>58004.7033828571</v>
       </c>
       <c r="G43" s="3">
-        <v>6.4961287851436502</v>
+        <v>5.8004703382857098E-2</v>
       </c>
       <c r="H43" s="3">
-        <v>1077132.3708939799</v>
+        <v>10470.72626908</v>
       </c>
       <c r="I43" s="3">
-        <v>3054.12730848315</v>
+        <v>4833.7252819047599</v>
       </c>
       <c r="J43" s="3">
-        <v>506.40920117253302</v>
+        <v>872.56052242333305</v>
       </c>
       <c r="K43" s="3">
-        <v>75.961380175879896</v>
+        <v>130.88407836350001</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -2581,37 +2581,40 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C44">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="D44">
-        <v>657</v>
+        <v>2</v>
       </c>
       <c r="E44" s="3">
-        <v>77911.958728638696</v>
+        <v>161.85990131080001</v>
       </c>
       <c r="F44" s="3">
-        <v>3858107.7875498701</v>
+        <v>8002.3153219047599</v>
       </c>
       <c r="G44" s="3">
-        <v>3.8581077875498702</v>
+        <v>8.0023153219047592E-3</v>
       </c>
       <c r="H44" s="3">
-        <v>519413.05819092499</v>
+        <v>1079.06600873867</v>
       </c>
       <c r="I44" s="3">
-        <v>5872.3101789191396</v>
+        <v>4001.15766095238</v>
       </c>
       <c r="J44" s="3">
-        <v>790.58304138649203</v>
+        <v>539.53300436933296</v>
       </c>
       <c r="K44" s="3">
-        <v>118.587456207974</v>
+        <v>80.929950655400006</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K44">
+    <sortCondition descending="1" ref="E2:E44"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>